--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T19:26:10+00:00</t>
+    <t>2026-09-03T19:45:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T19:45:41+00:00</t>
+    <t>2026-09-03T20:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T20:03:19+00:00</t>
+    <t>2026-09-05T06:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T06:23:19+00:00</t>
+    <t>2026-09-06T20:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.7.0</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:54:45+00:00</t>
+    <t>2026-09-06T21:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T21:15:57+00:00</t>
+    <t>2026-09-06T21:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T21:42:10+00:00</t>
+    <t>2026-09-07T08:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:34:40+00:00</t>
+    <t>2026-09-07T09:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:06:36+00:00</t>
+    <t>2026-09-07T09:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:30:32+00:00</t>
+    <t>2026-09-07T13:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/StructureDefinition-mii-pr-pro-promis-cognitive-function-sf4a-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T13:05:14+00:00</t>
+    <t>2026-09-07T13:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
